--- a/p6_deployment/data/germany/data_preparation/format_data/df_match_form.xlsx
+++ b/p6_deployment/data/germany/data_preparation/format_data/df_match_form.xlsx
@@ -429,71 +429,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>referee</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>venue</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>capacity</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>attendance</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>id_team_home</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>team_home</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>id_team_away</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>team_away</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
@@ -502,505 +512,1632 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>r7QOmnxn</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>45430.4375</v>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jollenbeck M. (Ger)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>BayArena (Leverkusen)</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>30210</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Leuna Chemie Stadion
+ (Halle)</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>15057</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>boX3cIQa</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>59</v>
-      </c>
-      <c r="L2" t="n">
-        <v>591</v>
+          <t>Hallescher</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="N2" t="n">
-        <v>20232024</v>
+        <v>593</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>20242025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fBoFTriU</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45430.4375</v>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Siebert D. (Ger)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Signal Iduna Park (Dortmund)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>81365</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>BRITA-Arena
+ (Wiesbaden)</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>12566</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>ObxFt3lm</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Darmstadt</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>59</v>
-      </c>
-      <c r="L3" t="n">
-        <v>591</v>
+          <t>Wehen</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="N3" t="n">
-        <v>20232024</v>
+        <v>593</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>20242025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QVFTn6ih</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45430.4375</v>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Zwayer F. (Ger)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Deutsche Bank Park (Frankfurt)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>58000</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Flyeralarm Arena
+ (Wurzburger)</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>13090</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>nVM1YUFj</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>59</v>
-      </c>
-      <c r="L4" t="n">
-        <v>591</v>
+          <t>Wurzburger Kickers</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="N4" t="n">
-        <v>20232024</v>
+        <v>593</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>20242025</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8EBlrr6N</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45430.4375</v>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Welz T. (Ger)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Voith-Arena (Heidenheim)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>15000</v>
-      </c>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>45520.65625</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>tbC3EcQn</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>FC Koln</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>59</v>
-      </c>
-      <c r="L5" t="n">
-        <v>591</v>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="N5" t="n">
-        <v>20232024</v>
+        <v>593</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>20242025</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YeJyopM4</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45430.4375</v>
+          <t>0K2qBFNG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fritz M. (Ger)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PreZero Arena (Sinsheim)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>30150</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>45521.33333333334</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Erzgebirgsstadion
+ (Aue)</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>16485</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>vsXIDreP</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>59</v>
-      </c>
-      <c r="L6" t="n">
-        <v>591</v>
+          <t>Aue</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="N6" t="n">
-        <v>20232024</v>
+        <v>593</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>20242025</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fB7pqOjH</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45430.4375</v>
+          <t>Kj4sifWp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Schlager D. (Ger)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MHPArena (Stuttgart)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>60449</v>
-      </c>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>45521.33333333334</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>WzEYqEyg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>59</v>
-      </c>
-      <c r="L7" t="n">
-        <v>591</v>
+          <t>Schott Mainz</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="N7" t="n">
-        <v>20232024</v>
+        <v>593</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>20242025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WWMKlSMu</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45430.4375</v>
+          <t>bF2q76Mr</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dingert C. (Ger)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stadion An der Alten Försterei (Berlin)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>22012</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Union Berlin</t>
-        </is>
-      </c>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>OSTALB ARENA
+ (Aalen)</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>14500</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>Oh2C15j0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>59</v>
-      </c>
-      <c r="L8" t="n">
-        <v>591</v>
+          <t>Aalen</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Schalke</t>
+        </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="N8" t="n">
-        <v>20232024</v>
+        <v>593</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>20242025</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CnIup4yB</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45430.4375</v>
+          <t>vyk5gjdE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Petersen M. (Ger)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Weserstadion (Bremen)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>42100</v>
-      </c>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>Q1yNyI5t</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>59</v>
-      </c>
-      <c r="L9" t="n">
-        <v>591</v>
+          <t>Greifswald</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="N9" t="n">
-        <v>20232024</v>
+        <v>593</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>20242025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4MEXoQ6b</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45430.4375</v>
+          <t>tbKZHNz1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Willenborg F. (Ger)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Volkswagen Arena (Wolfsburg)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>28917</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Audi Sportpark
+ (Ingolstadt)</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>15800</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>ne5QkLtB</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>59</v>
-      </c>
-      <c r="L10" t="n">
-        <v>591</v>
+          <t>Ingolstadt</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="N10" t="n">
-        <v>20232024</v>
+        <v>593</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>MZjh9ghT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stadion an der Hafenstrasse
+ (Essen)</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>20352</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>EB0xsr77</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>RW Essen</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>59</v>
+      </c>
+      <c r="N11" t="n">
+        <v>593</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>f1nnRRDE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>88Xgj1Y5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>VfL Osnabruck</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>59</v>
+      </c>
+      <c r="N12" t="n">
+        <v>593</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8QPARz8c</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>lKLJUxeT</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Villingen</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>59</v>
+      </c>
+      <c r="N13" t="n">
+        <v>593</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hzyf0b9b</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>45521.54166666666</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>New Tivoli
+ (Aachen)</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>31026</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>j3PKcB4E</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Alemannia Aachen</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>59</v>
+      </c>
+      <c r="N14" t="n">
+        <v>593</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CpiTEcOi</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>45521.54166666666</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Schüco Arena
+ (Bielefeld)</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>27332</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pp38UXK8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Arminia Bielefeld</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>59</v>
+      </c>
+      <c r="N15" t="n">
+        <v>593</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8CpxDyg4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>45521.54166666666</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stadion Lohmühle
+ (Lubeck)</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>17849</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>I1Vk6k3R</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Phonix Lubeck</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>59</v>
+      </c>
+      <c r="N16" t="n">
+        <v>593</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6q2yrHgU</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>45522.33333333334</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ludwigspark Stadion
+ (Saarbrücken)</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>16003</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>fLbhmJ5l</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Saarbrucken</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Nurnberg</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>59</v>
+      </c>
+      <c r="N17" t="n">
+        <v>593</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AiJ3kset</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>45522.33333333334</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>UNr2EUfd</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Viktoria Berlin</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>59</v>
+      </c>
+      <c r="N18" t="n">
+        <v>593</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>YV3TqwPH</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>tW75B1ei</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Bremer</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>59</v>
+      </c>
+      <c r="N19" t="n">
+        <v>593</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>l0ueP5rR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ostseestadion
+ (Rostock)</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>KIHmtCkL</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Hansa Rostock</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>59</v>
+      </c>
+      <c r="N20" t="n">
+        <v>593</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>t2AoZLAa</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>E3xs5mIe</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Hildesheim</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>59</v>
+      </c>
+      <c r="N21" t="n">
+        <v>593</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>jFMCm08e</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jahnstadion Regensburg
+ (Regensburg)</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>15210</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>59</v>
+      </c>
+      <c r="N22" t="n">
+        <v>593</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Hardtwaldstadion
+ (Sandhausen)</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>15414</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>UZxEj1R4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sandhausen</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>59</v>
+      </c>
+      <c r="N23" t="n">
+        <v>593</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>WrbkcjCd</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Teutonia Ottensen</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>59</v>
+      </c>
+      <c r="N24" t="n">
+        <v>593</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>45522.54166666666</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>hjNlCFPB</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Lotte</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>59</v>
+      </c>
+      <c r="N25" t="n">
+        <v>593</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>45522.54166666666</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Hansch-Arena
+ (Meppen)</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>13696</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>rXqBh2xP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Meppen</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>59</v>
+      </c>
+      <c r="N26" t="n">
+        <v>593</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>45522.54166666666</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rudolf-Harbig-Stadion
+ (Dresden)</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>32249</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>zL1YsOi1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>SG Dynamo Dresden</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>59</v>
+      </c>
+      <c r="N27" t="n">
+        <v>593</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>fcxqFy2l</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Super Cup</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>30210</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>59</v>
+      </c>
+      <c r="N28" t="n">
+        <v>594</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2024</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/germany/data_preparation/format_data/df_match_form.xlsx
+++ b/p6_deployment/data/germany/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -718,8 +718,15 @@
         <v>45520.65625</v>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Donaustadion
+ (Ulm)</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>19500</v>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
@@ -956,8 +963,15 @@
         <v>45521.4375</v>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Volksstadion Greifswald
+ (Greifswald)</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4990</v>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
@@ -1138,8 +1152,15 @@
         <v>45521.4375</v>
       </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stadion an der Bremer Brück
+ (Osnabrück)</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>16667</v>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
@@ -1194,8 +1215,15 @@
         <v>45521.4375</v>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>MS Technologie Arena
+ (Villingen-Schwenningen)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>8000</v>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
@@ -1677,8 +1705,15 @@
         <v>45522.4375</v>
       </c>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Friedrich-Ebert-Stadium
+ (Hildesheim)</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>10000</v>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
@@ -1915,8 +1950,15 @@
         <v>45522.54166666666</v>
       </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Stadion am Lotter Kreuz
+ (Lotte)</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>10059</v>
+      </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
@@ -2080,7 +2122,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>fcxqFy2l</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2090,53 +2132,305 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Super Cup</t>
+          <t>DFB Pokal</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
+          <t>Stadion der Freundschaft
+ (Cottbus)</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>22450</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6g44VD52</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Cottbus</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>59</v>
+      </c>
+      <c r="N28" t="n">
+        <v>593</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bieberer Berg Stadion
+ (Offenbach am Main)</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>20500</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>YJURlaIO</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Offenbach</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>59</v>
+      </c>
+      <c r="N29" t="n">
+        <v>593</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stadion Oberwerth
+ (Koblenz)</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>9500</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>p8wBsqZt</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>TuS Koblenz</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>59</v>
+      </c>
+      <c r="N30" t="n">
+        <v>593</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>45523.65625</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Eintracht-Stadion
+ (Braunschweig)</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>23325</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>59</v>
+      </c>
+      <c r="N31" t="n">
+        <v>593</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>20242025</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>fcxqFy2l</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Super Cup</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>BayArena
  (Leverkusen)</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="G32" t="n">
         <v>30210</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
         <is>
           <t>4jcj2zMd</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Bayer Leverkusen</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="M28" t="n">
-        <v>59</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="M32" t="n">
+        <v>59</v>
+      </c>
+      <c r="N32" t="n">
         <v>594</v>
       </c>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
         <v>2024</v>
       </c>
     </row>
